--- a/outputs/analysis/Metformin/extracted_trials/DPP_Extended_Cohort_extracted.xlsx
+++ b/outputs/analysis/Metformin/extracted_trials/DPP_Extended_Cohort_extracted.xlsx
@@ -140,6 +140,216 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -502,26 +712,18 @@
           <t>RCT_METFORMIN_DPP</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>2012</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -535,6 +737,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -548,6 +751,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -561,6 +765,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -644,7 +849,6 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>age hemoglobin and hematocrit levels were slightly lower in the  hemoglobin and hematocrit levels were slightly lower in the</t>
@@ -680,7 +884,6 @@
       <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>age of of</t>
@@ -716,7 +919,6 @@
       <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>age 2.1-kg weight loss (4). 2.1-kg weight loss (4).</t>
@@ -752,7 +954,6 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>age 2.5-kg weight loss over 2.5-kg weight loss over</t>
@@ -788,7 +989,6 @@
       <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>age of 3.2 of 3.2</t>
@@ -824,7 +1024,6 @@
       <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>aged to join the DPPOS, and 88% did to join the DPPOS, and 88% did</t>
@@ -860,7 +1059,6 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>aged
@@ -897,7 +1095,6 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>age losing losing</t>
@@ -933,7 +1130,6 @@
       <c r="F10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>age weight of weight of</t>
@@ -969,7 +1165,6 @@
       <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>age weight loss from baseline in weight loss from baseline in</t>
@@ -1005,7 +1200,6 @@
       <c r="F12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>age 28% vs. 16%, 28% vs. 16%,</t>
@@ -1041,7 +1235,6 @@
       <c r="F13" t="n">
         <v>4</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>age hemoglobin hemoglobin</t>
@@ -1077,7 +1270,6 @@
       <c r="F14" t="n">
         <v>7</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>age XR) in type 2 diabetic pa- XR) in type 2 diabetic pa-</t>
@@ -1086,6 +1278,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1146,7 +1339,6 @@
           <t>ISS_0001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Studies</t>
@@ -1184,7 +1376,6 @@
           <t>ISS_0002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Provenance</t>
@@ -1218,6 +1409,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1231,5 +1423,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>